--- a/contributions.xlsx
+++ b/contributions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/awoelfl/Workspaces/internet-technologies/project/docs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rashe\group_b\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D26F744-8CA5-184F-954B-323BA98AFBC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0977D0E0-A8F9-45BB-BAD4-86B9CE165491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45400" yWindow="600" windowWidth="23380" windowHeight="28180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Internet Technologies Project</t>
   </si>
@@ -51,58 +51,53 @@
     <t>Ownership</t>
   </si>
   <si>
-    <t>John</t>
-  </si>
-  <si>
-    <t>Doe</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Example</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>:</t>
-    </r>
-  </si>
-  <si>
-    <t>Andreas</t>
-  </si>
-  <si>
-    <t>Wölfl</t>
-  </si>
-  <si>
-    <t>andreas.woelfl@th-deg.de</t>
-  </si>
-  <si>
-    <t>Conversation Engine, React Components, Fallback</t>
-  </si>
-  <si>
     <t>Keyword Spotting, Conversation Engine, Design &amp; Layout, React Components, Export, Extensibility, Fallback, Reset</t>
   </si>
   <si>
-    <t>john@th-deg.de</t>
-  </si>
-  <si>
     <t>Features:</t>
+  </si>
+  <si>
+    <t>Esther</t>
+  </si>
+  <si>
+    <t>Mpofu</t>
+  </si>
+  <si>
+    <t>esther.mpofu@stud.th-deg.de</t>
+  </si>
+  <si>
+    <t>Subin</t>
+  </si>
+  <si>
+    <t>Samu</t>
+  </si>
+  <si>
+    <t>subin.samu@th-deg.de</t>
+  </si>
+  <si>
+    <t>Adhinkrishna</t>
+  </si>
+  <si>
+    <t>Kottarathil Unnikrishnan</t>
+  </si>
+  <si>
+    <t>adhinkrishna.kottarathil-unnikrishnan@th-deg.de</t>
+  </si>
+  <si>
+    <t>Abin</t>
+  </si>
+  <si>
+    <t>Toby</t>
+  </si>
+  <si>
+    <t>abin.-2@th-deg.de</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -129,12 +124,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -175,7 +164,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -581,16 +570,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.1640625" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" customWidth="1"/>
-    <col min="3" max="3" width="23.5" customWidth="1"/>
+    <col min="1" max="1" width="15.109375" customWidth="1"/>
+    <col min="2" max="2" width="22.77734375" customWidth="1"/>
+    <col min="3" max="3" width="42.21875" customWidth="1"/>
     <col min="4" max="4" width="11.33203125" customWidth="1"/>
-    <col min="5" max="5" width="122.1640625" customWidth="1"/>
+    <col min="5" max="5" width="122.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="22.8" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -599,7 +588,7 @@
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -607,13 +596,13 @@
         <v>2</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
@@ -630,89 +619,75 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6">
+        <v>22591601</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7">
+        <v>22402289</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>16</v>
       </c>
-      <c r="D6">
-        <v>12345678</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7">
-        <v>12345678</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D8">
-        <v>12345678</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+        <v>12639648</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D9">
-        <v>12345678</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A13" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14">
-        <v>20144287</v>
-      </c>
-      <c r="E14" t="s">
-        <v>14</v>
-      </c>
+        <v>12636389</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C14" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="C14" r:id="rId2" xr:uid="{FA90D88F-9C40-664E-89C4-CABEA0645AE4}"/>
-    <hyperlink ref="C7:C9" r:id="rId3" display="john@th-deg.de" xr:uid="{D048D7F0-AB26-6E49-A75B-A31E8097A42B}"/>
+    <hyperlink ref="C6" r:id="rId1" xr:uid="{8EDB328A-856C-4328-A707-F874C0B969D0}"/>
+    <hyperlink ref="C7:C9" r:id="rId2" display="john@th-deg.de" xr:uid="{1C4114D9-B8A8-42B1-94C9-9E564FC3DB2C}"/>
+    <hyperlink ref="C7" r:id="rId3" xr:uid="{E7454312-BCBA-45B1-88D2-A8703EE45E61}"/>
+    <hyperlink ref="C8" r:id="rId4" xr:uid="{2D69B81D-2259-480A-A605-0E19808E03F7}"/>
+    <hyperlink ref="C9" r:id="rId5" xr:uid="{4ACEF15E-90C5-438F-AA7D-A6E1D44950E7}"/>
   </hyperlinks>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>

--- a/contributions.xlsx
+++ b/contributions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rashe\group_b\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0977D0E0-A8F9-45BB-BAD4-86B9CE165491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1379BAD6-7325-475B-AC6F-B43FDA411376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,9 +33,6 @@
     <t>Group Name:</t>
   </si>
   <si>
-    <t>ACME Group</t>
-  </si>
-  <si>
     <t>Firstname</t>
   </si>
   <si>
@@ -91,6 +88,9 @@
   </si>
   <si>
     <t>abin.-2@th-deg.de</t>
+  </si>
+  <si>
+    <t>Group B</t>
   </si>
 </sst>
 </file>
@@ -593,41 +593,41 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>6</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" s="6" t="s">
         <v>11</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>12</v>
       </c>
       <c r="D6">
         <v>22591601</v>
@@ -635,13 +635,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
         <v>13</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" s="6" t="s">
         <v>14</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>15</v>
       </c>
       <c r="D7">
         <v>22402289</v>
@@ -649,13 +649,13 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
         <v>16</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" s="6" t="s">
         <v>17</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>18</v>
       </c>
       <c r="D8">
         <v>12639648</v>
@@ -663,13 +663,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
         <v>19</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>21</v>
       </c>
       <c r="D9">
         <v>12636389</v>
